--- a/4519 Chugai.xlsx
+++ b/4519 Chugai.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70469DA4-039F-4322-A393-709F309F8903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92595E9A-15F5-4E8B-9504-C24E00B539ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27435" yWindow="1140" windowWidth="26490" windowHeight="19650" xr2:uid="{3564809F-01A6-46D3-96C5-46308A521655}"/>
+    <workbookView xWindow="1440" yWindow="4690" windowWidth="19050" windowHeight="16100" xr2:uid="{3564809F-01A6-46D3-96C5-46308A521655}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="132">
   <si>
     <t>Price JPY</t>
   </si>
@@ -430,6 +430,9 @@
   </si>
   <si>
     <t>Q424</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -960,18 +963,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C587E22-4E4C-49B0-BEBE-68FEA42F09BE}">
   <dimension ref="B2:K35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="2" max="2" width="23.7265625" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" customWidth="1"/>
+    <col min="6" max="6" width="10.7265625" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
+    <col min="10" max="10" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>71</v>
       </c>
@@ -994,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>6936</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+        <v>7416</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>104</v>
       </c>
@@ -1012,13 +1015,13 @@
         <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>1645.3926369999999</v>
+        <v>1679.057667</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>103</v>
       </c>
@@ -1034,10 +1037,10 @@
       </c>
       <c r="J4" s="1">
         <f>+J2*J3</f>
-        <v>11412443.330232</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+        <v>12451891.658472</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>54</v>
       </c>
@@ -1052,13 +1055,14 @@
         <v>3</v>
       </c>
       <c r="J5" s="1">
-        <v>815658</v>
+        <f>390439+572134</f>
+        <v>962573</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>102</v>
       </c>
@@ -1076,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>56</v>
       </c>
@@ -1092,10 +1096,10 @@
       </c>
       <c r="J7" s="1">
         <f>+J4-J5+J6</f>
-        <v>10596785.330232</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+        <v>11489318.658472</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>57</v>
       </c>
@@ -1107,7 +1111,7 @@
       </c>
       <c r="G8" s="10"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>58</v>
       </c>
@@ -1119,7 +1123,7 @@
       </c>
       <c r="G9" s="10"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>97</v>
       </c>
@@ -1131,7 +1135,7 @@
       </c>
       <c r="G10" s="10"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>94</v>
       </c>
@@ -1143,7 +1147,7 @@
       </c>
       <c r="G11" s="10"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>61</v>
       </c>
@@ -1152,7 +1156,7 @@
       </c>
       <c r="G12" s="10"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>101</v>
       </c>
@@ -1161,7 +1165,7 @@
       </c>
       <c r="G13" s="10"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>63</v>
       </c>
@@ -1173,7 +1177,7 @@
       </c>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>87</v>
       </c>
@@ -1182,7 +1186,7 @@
       </c>
       <c r="G15" s="10"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>90</v>
       </c>
@@ -1194,37 +1198,37 @@
       </c>
       <c r="G16" s="10"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="10"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>66</v>
       </c>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>67</v>
       </c>
       <c r="G19" s="10"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
         <v>70</v>
       </c>
@@ -1234,7 +1238,7 @@
       <c r="F22" s="12"/>
       <c r="G22" s="13"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -1244,7 +1248,7 @@
       <c r="F23" s="7"/>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>121</v>
       </c>
@@ -1256,49 +1260,49 @@
       </c>
       <c r="G24" s="10"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G25" s="10"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>106</v>
       </c>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>107</v>
       </c>
       <c r="G27" s="10"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>108</v>
       </c>
       <c r="G28" s="10"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>109</v>
       </c>
       <c r="G29" s="10"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G30" s="10"/>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>111</v>
       </c>
       <c r="G31" s="10"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>115</v>
       </c>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="G32" s="10"/>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>117</v>
       </c>
@@ -1322,7 +1326,7 @@
       </c>
       <c r="G33" s="10"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>113</v>
       </c>
@@ -1331,7 +1335,7 @@
       </c>
       <c r="G34" s="10"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="11" t="s">
         <v>112</v>
       </c>
@@ -1350,23 +1354,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116815EA-00C2-4327-B106-FFC6B3AC13D1}">
   <dimension ref="A1:W67"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="9.140625" style="2"/>
-    <col min="12" max="12" width="9.7109375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" style="2" customWidth="1"/>
-    <col min="14" max="15" width="9.140625" style="2"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="9.1796875" style="2"/>
+    <col min="12" max="12" width="9.7265625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.453125" style="2" customWidth="1"/>
+    <col min="14" max="15" width="9.1796875" style="2"/>
     <col min="21" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
@@ -1431,7 +1435,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>61</v>
       </c>
@@ -1468,7 +1472,7 @@
         <v>81200</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
@@ -1514,7 +1518,7 @@
         <v>58400</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>63</v>
       </c>
@@ -1560,7 +1564,7 @@
         <v>41700</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>52</v>
       </c>
@@ -1597,7 +1601,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>53</v>
       </c>
@@ -1634,7 +1638,7 @@
         <v>15100</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>55</v>
       </c>
@@ -1680,7 +1684,7 @@
         <v>23300</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1725,7 +1729,7 @@
         <v>16800</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>54</v>
       </c>
@@ -1762,7 +1766,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>56</v>
       </c>
@@ -1799,7 +1803,7 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>57</v>
       </c>
@@ -1836,7 +1840,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>58</v>
       </c>
@@ -1873,7 +1877,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>59</v>
       </c>
@@ -1910,7 +1914,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>60</v>
       </c>
@@ -1947,7 +1951,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>83</v>
       </c>
@@ -1984,7 +1988,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="17" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>64</v>
       </c>
@@ -2029,7 +2033,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="18" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>65</v>
       </c>
@@ -2066,7 +2070,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="19" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>66</v>
       </c>
@@ -2103,7 +2107,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="20" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>67</v>
       </c>
@@ -2140,7 +2144,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>68</v>
       </c>
@@ -2177,7 +2181,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="22" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>69</v>
       </c>
@@ -2209,7 +2213,7 @@
       </c>
       <c r="O22" s="3"/>
     </row>
-    <row r="23" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>70</v>
       </c>
@@ -2241,7 +2245,7 @@
       </c>
       <c r="O23" s="3"/>
     </row>
-    <row r="24" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>86</v>
       </c>
@@ -2278,7 +2282,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>84</v>
       </c>
@@ -2315,7 +2319,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="26" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -2330,7 +2334,7 @@
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
     </row>
-    <row r="27" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
@@ -2368,7 +2372,7 @@
         <v>291600</v>
       </c>
     </row>
-    <row r="28" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2402,7 +2406,7 @@
       </c>
       <c r="O28" s="3"/>
     </row>
-    <row r="29" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2434,7 +2438,7 @@
         <v>20700</v>
       </c>
     </row>
-    <row r="30" spans="2:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:21" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>8</v>
       </c>
@@ -2494,7 +2498,7 @@
         <v>552860</v>
       </c>
     </row>
-    <row r="31" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>24</v>
       </c>
@@ -2524,7 +2528,7 @@
       </c>
       <c r="O31" s="3"/>
     </row>
-    <row r="32" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>25</v>
       </c>
@@ -2557,7 +2561,7 @@
       </c>
       <c r="O32" s="3"/>
     </row>
-    <row r="33" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2587,7 +2591,7 @@
       </c>
       <c r="O33" s="3"/>
     </row>
-    <row r="34" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2617,7 +2621,7 @@
       </c>
       <c r="O34" s="3"/>
     </row>
-    <row r="35" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2647,7 +2651,7 @@
       </c>
       <c r="O35" s="3"/>
     </row>
-    <row r="36" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O36" s="3"/>
     </row>
-    <row r="37" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>27</v>
       </c>
@@ -2713,7 +2717,7 @@
       </c>
       <c r="O37" s="3"/>
     </row>
-    <row r="38" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>34</v>
       </c>
@@ -2743,7 +2747,7 @@
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
     </row>
-    <row r="39" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>33</v>
       </c>
@@ -2776,7 +2780,7 @@
       </c>
       <c r="O39" s="3"/>
     </row>
-    <row r="40" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,7 +2808,7 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
     </row>
-    <row r="41" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>31</v>
       </c>
@@ -2837,7 +2841,7 @@
       </c>
       <c r="O41" s="3"/>
     </row>
-    <row r="45" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>36</v>
       </c>
@@ -2865,7 +2869,7 @@
         <v>815658</v>
       </c>
     </row>
-    <row r="46" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>37</v>
       </c>
@@ -2890,7 +2894,7 @@
         <v>44426</v>
       </c>
     </row>
-    <row r="47" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>38</v>
       </c>
@@ -2918,7 +2922,7 @@
         <v>66344</v>
       </c>
     </row>
-    <row r="48" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
         <v>39</v>
       </c>
@@ -2943,7 +2947,7 @@
         <v>349656</v>
       </c>
     </row>
-    <row r="49" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>40</v>
       </c>
@@ -2968,7 +2972,7 @@
         <v>265704</v>
       </c>
     </row>
-    <row r="50" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>35</v>
       </c>
@@ -2993,7 +2997,7 @@
         <v>420292</v>
       </c>
     </row>
-    <row r="51" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>45</v>
       </c>
@@ -3018,7 +3022,7 @@
         <v>59797</v>
       </c>
     </row>
-    <row r="52" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>44</v>
       </c>
@@ -3043,7 +3047,7 @@
         <v>7995</v>
       </c>
     </row>
-    <row r="53" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>43</v>
       </c>
@@ -3068,7 +3072,7 @@
         <v>20350</v>
       </c>
     </row>
-    <row r="54" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>42</v>
       </c>
@@ -3093,7 +3097,7 @@
         <v>9941</v>
       </c>
     </row>
-    <row r="55" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>41</v>
       </c>
@@ -3147,7 +3151,7 @@
         <v>2060163</v>
       </c>
     </row>
-    <row r="57" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>46</v>
       </c>
@@ -3172,7 +3176,7 @@
         <v>136084</v>
       </c>
     </row>
-    <row r="58" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>47</v>
       </c>
@@ -3197,7 +3201,7 @@
         <v>78954</v>
       </c>
     </row>
-    <row r="59" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>48</v>
       </c>
@@ -3225,7 +3229,7 @@
         <v>10215</v>
       </c>
     </row>
-    <row r="60" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
         <v>38</v>
       </c>
@@ -3251,7 +3255,7 @@
         <v>72689</v>
       </c>
     </row>
-    <row r="61" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>51</v>
       </c>
@@ -3276,7 +3280,7 @@
         <v>6582</v>
       </c>
     </row>
-    <row r="62" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>44</v>
       </c>
@@ -3301,7 +3305,7 @@
         <v>3949</v>
       </c>
     </row>
-    <row r="63" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
         <v>50</v>
       </c>
@@ -3326,7 +3330,7 @@
         <v>1751691</v>
       </c>
     </row>
-    <row r="64" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>49</v>
       </c>
@@ -3354,7 +3358,7 @@
         <v>2060164</v>
       </c>
     </row>
-    <row r="67" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
         <v>85</v>
       </c>
